--- a/nriss-patch-2/ig/StructureDefinition-fr-specimen-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-specimen-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:15:45+00:00</t>
+    <t>2026-10-01T07:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -546,7 +546,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-specimen-type-cisis|20260619134042</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-specimen-type-cisis|20260916095454</t>
   </si>
   <si>
     <t>.code</t>
